--- a/tabtools/demo/demo_hrcomptab.xlsx
+++ b/tabtools/demo/demo_hrcomptab.xlsx
@@ -270,7 +270,7 @@
     <t>0.11</t>
   </si>
   <si>
-    <t>"Demo of hrcomptab. The stratetab frame supplies events, person-years, and rates; selected regtab rows supply adjusted hazard ratios and p-values."</t>
+    <t>Demo of hrcomptab. The stratetab frame supplies events, person-years, and rates; selected regtab rows supply adjusted hazard ratios and p-values.</t>
   </si>
 </sst>
 </file>

--- a/tabtools/demo/demo_hrcomptab.xlsx
+++ b/tabtools/demo/demo_hrcomptab.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="188" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="188" uniqueCount="88">
   <si>
     <t>Table 19. Hormone Therapy Events, Person-Years, and Adjusted Hazard Ratios</t>
   </si>
@@ -108,28 +108,31 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>0.77 (0.30, 2.01)</t>
+    <t>0.80 (0.35, 1.86)</t>
   </si>
   <si>
-    <t>1.27 (0.43, 3.76)</t>
+    <t>3.25 (0.67, 15.71)</t>
   </si>
   <si>
-    <t>0.75 (0.21, 2.68)</t>
+    <t>2.12 (0.39, 11.63)</t>
   </si>
   <si>
-    <t>0.60 (0.17, 2.12)</t>
+    <t>1.88 (0.34, 10.41)</t>
   </si>
   <si>
     <t>p-value</t>
   </si>
   <si>
-    <t>0.59</t>
+    <t>0.61</t>
   </si>
   <si>
-    <t>0.66</t>
+    <t>0.14</t>
   </si>
   <si>
-    <t>0.43</t>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>0.47</t>
   </si>
   <si>
     <t>Sustained EDSS 6</t>
@@ -180,25 +183,28 @@
     <t>1.2 (0.3-4.7)</t>
   </si>
   <si>
-    <t>0.95 (0.24, 3.79)</t>
+    <t>0.50 (0.14, 1.81)</t>
   </si>
   <si>
-    <t>0.39 (0.10, 1.53)</t>
+    <t>0.31 (0.03, 3.05)</t>
   </si>
   <si>
-    <t>0.00</t>
+    <t>1.18 (0.26, 5.40)</t>
   </si>
   <si>
-    <t>0.48 (0.14, 1.63)</t>
+    <t>0.17 (0.02, 1.86)</t>
   </si>
   <si>
-    <t>0.94</t>
+    <t>0.29</t>
   </si>
   <si>
-    <t>0.18</t>
+    <t>0.32</t>
   </si>
   <si>
-    <t>0.24</t>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>0.15</t>
   </si>
   <si>
     <t>Recurring Relapse</t>
@@ -246,28 +252,28 @@
     <t>9.0 (5.5-15.0)</t>
   </si>
   <si>
-    <t>1.00 (0.56, 1.76)</t>
+    <t>0.60 (0.35, 1.04)</t>
   </si>
   <si>
-    <t>0.41 (0.19, 0.90)</t>
+    <t>1.29 (0.61, 2.71)</t>
   </si>
   <si>
-    <t>0.66 (0.33, 1.33)</t>
+    <t>1.37 (0.65, 2.88)</t>
   </si>
   <si>
-    <t>0.57 (0.28, 1.14)</t>
+    <t>1.19 (0.56, 2.53)</t>
   </si>
   <si>
-    <t>0.99</t>
+    <t>0.067</t>
   </si>
   <si>
-    <t>0.026</t>
+    <t>0.50</t>
   </si>
   <si>
-    <t>0.25</t>
+    <t>0.41</t>
   </si>
   <si>
-    <t>0.11</t>
+    <t>0.64</t>
   </si>
   <si>
     <t>Demo of hrcomptab. The stratetab frame supplies events, person-years, and rates; selected regtab rows supply adjusted hazard ratios and p-values.</t>
@@ -11657,7 +11663,7 @@
     <col min="3" max="3" width="7.7109375" style="4" customWidth="true"/>
     <col min="4" max="4" width="16.7109375" style="5" customWidth="true"/>
     <col min="5" max="5" width="19.7109375" style="6" customWidth="true"/>
-    <col min="6" max="6" width="15.7109375" style="7" customWidth="true"/>
+    <col min="6" max="6" width="16.7109375" style="7" customWidth="true"/>
     <col min="7" max="7" width="7.7109375" style="8" customWidth="true"/>
     <col min="8" max="8" width="7.7109375" style="9" customWidth="true"/>
     <col min="9" max="9" width="16.7109375" style="10" customWidth="true"/>
@@ -11747,7 +11753,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="341" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="342" t="s">
         <v>1</v>
@@ -11762,7 +11768,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="346" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N2" s="347" t="s">
         <v>1</v>
@@ -11906,13 +11912,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="451" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I5" s="452" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J5" s="453" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K5" s="454" t="s">
         <v>30</v>
@@ -11921,13 +11927,13 @@
         <v>1</v>
       </c>
       <c r="M5" s="456" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N5" s="457" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O5" s="458" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P5" s="459" t="s">
         <v>30</v>
@@ -11959,34 +11965,34 @@
         <v>36</v>
       </c>
       <c r="H6" s="607" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="608" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J6" s="609" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K6" s="610" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L6" s="611" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M6" s="612" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N6" s="613" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O6" s="614" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P6" s="615" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q6" s="616" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
@@ -12065,13 +12071,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="496" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I8" s="497" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J8" s="498" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K8" s="499" t="s">
         <v>30</v>
@@ -12080,13 +12086,13 @@
         <v>1</v>
       </c>
       <c r="M8" s="501" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N8" s="502" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O8" s="503" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P8" s="504" t="s">
         <v>30</v>
@@ -12118,34 +12124,34 @@
         <v>37</v>
       </c>
       <c r="H9" s="511" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I9" s="512" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J9" s="513" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K9" s="514" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L9" s="588" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M9" s="516" t="s">
         <v>13</v>
       </c>
       <c r="N9" s="517" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O9" s="518" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P9" s="519" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q9" s="598" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -12168,37 +12174,37 @@
         <v>33</v>
       </c>
       <c r="G10" s="579" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H10" s="526" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I10" s="527" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J10" s="528" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K10" s="529" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L10" s="589" t="s">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="M10" s="531" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N10" s="532" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O10" s="533" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P10" s="534" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q10" s="599" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
@@ -12221,42 +12227,42 @@
         <v>34</v>
       </c>
       <c r="G11" s="622" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11" s="623" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I11" s="624" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J11" s="625" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K11" s="626" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L11" s="627" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M11" s="628" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N11" s="629" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O11" s="630" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P11" s="631" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q11" s="632" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="637" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C12" s="0"/>
       <c r="D12" s="0"/>

--- a/tabtools/demo/demo_hrcomptab.xlsx
+++ b/tabtools/demo/demo_hrcomptab.xlsx
@@ -87,19 +87,19 @@
     <t>Per 1,000 PY (95% CI)</t>
   </si>
   <si>
-    <t>8.1 (6.1-10.7)</t>
+    <t>8.1 (6.1, 10.7)</t>
   </si>
   <si>
-    <t>6.2 (4.4-8.9)</t>
+    <t>6.2 (4.4, 8.9)</t>
   </si>
   <si>
-    <t>9.1 (5.6-14.8)</t>
+    <t>9.1 (5.6, 14.8)</t>
   </si>
   <si>
-    <t>6.0 (3.1-11.4)</t>
+    <t>6.0 (3.1, 11.4)</t>
   </si>
   <si>
-    <t>3.5 (1.6-7.8)</t>
+    <t>3.5 (1.6, 7.8)</t>
   </si>
   <si>
     <t>aHR (95% CI)</t>
@@ -168,19 +168,19 @@
     <t>1,700</t>
   </si>
   <si>
-    <t>3.6 (2.3-5.6)</t>
+    <t>3.6 (2.3, 5.6)</t>
   </si>
   <si>
-    <t>2.4 (1.4-4.2)</t>
+    <t>2.4 (1.4, 4.2)</t>
   </si>
   <si>
-    <t>3.9 (1.9-8.1)</t>
+    <t>3.9 (1.9, 8.1)</t>
   </si>
   <si>
-    <t>2.0 (0.6-6.0)</t>
+    <t>2.0 (0.6, 6.0)</t>
   </si>
   <si>
-    <t>1.2 (0.3-4.7)</t>
+    <t>1.2 (0.3, 4.7)</t>
   </si>
   <si>
     <t>0.50 (0.14, 1.81)</t>
@@ -237,19 +237,19 @@
     <t>1,660</t>
   </si>
   <si>
-    <t>17.1 (13.8-21.1)</t>
+    <t>17.1 (13.8, 21.1)</t>
   </si>
   <si>
-    <t>13.7 (10.6-17.6)</t>
+    <t>13.7 (10.6, 17.6)</t>
   </si>
   <si>
-    <t>17.8 (12.5-25.3)</t>
+    <t>17.8 (12.5, 25.3)</t>
   </si>
   <si>
-    <t>14.1 (9.2-21.5)</t>
+    <t>14.1 (9.2, 21.5)</t>
   </si>
   <si>
-    <t>9.0 (5.5-15.0)</t>
+    <t>9.0 (5.5, 15.0)</t>
   </si>
   <si>
     <t>0.60 (0.35, 1.04)</t>
